--- a/results/gnn_rl_r2/bang_tong_hop_gnn_rl.xlsx
+++ b/results/gnn_rl_r2/bang_tong_hop_gnn_rl.xlsx
@@ -1472,7 +1472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1688,42 +1688,54 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rl_sac_no_gnn</t>
+          <t>odgraphformer_no_spatial_attn</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7434541613052</v>
+        <v>0.7627785243677492</v>
       </c>
       <c r="E4" t="n">
-        <v>5.502855413459399</v>
+        <v>5.640104853273177</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4625203508512</v>
+        <v>0.5004207742029969</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3069011960602</v>
+        <v>0.3080711544997622</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8650627234050476</v>
+        <v>0.8667205244170576</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7059696724195607</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>0.6514559222601297</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0008169903622961447</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07015797200121543</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.00136016738890838</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001468826576874904</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0001608426202975126</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.002947902353554886</v>
+      </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>RL-Gate: bỏ GNN</t>
+          <t>OD-GraphFormer: bỏ attention giữa luồng</t>
         </is>
       </c>
     </row>
@@ -1735,54 +1747,54 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>branch_odgraphformer</t>
+          <t>rl_sac_no_gnn</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.768482934427742</v>
+        <v>0.7324499461620667</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7123537593092</v>
+        <v>5.468607495383799</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5024813722540648</v>
+        <v>0.4505609488202333</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3086315974355888</v>
+        <v>0.3095732268565</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8675420811647035</v>
+        <v>0.8637099737891488</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6516442537487873</v>
+        <v>0.7660097805206326</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008202309350803816</v>
+        <v>0.01508006654970827</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03383439908779904</v>
+        <v>0.02966135059418695</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005420806961698338</v>
+        <v>0.01038397132690988</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003168122195565833</v>
+        <v>0.00286661210289679</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001108314726900352</v>
+        <v>0.002113997212412626</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006895948329105633</v>
+        <v>0.05203381006858283</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>OD-GraphFormer đầy đủ</t>
+          <t>RL-Gate: bỏ GNN</t>
         </is>
       </c>
     </row>
@@ -1794,52 +1806,229 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>rl_sac_no_oof</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7319508214811667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.471675044616366</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4570341028517333</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3053813118828</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8636252817450375</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7334137130735394</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.009982208343762662</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03225818847532842</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.006068809907354892</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0003484073481395493</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001181278707752452</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02595054690469781</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>RL-Gate: không dùng OOF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>geant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rl_sac_static_prior</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7223496481252334</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.454022071541599</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4469904437010334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3134659875636001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8612394714952375</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8102807460588579</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.004665156863395726</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0354066058991332</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0002751116433246551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.000710104055692522</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001467909444345737</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0002584864829614626</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>RL-Gate: prior tĩnh thay cho Hedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>geant</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>branch_odgraphformer</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.768482934427742</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.7123537593092</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5024813722540648</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3086315974355888</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8675420811647035</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6516442537487873</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.008202309350803816</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03383439908779904</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.005420806961698338</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.003168122195565833</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001108314726900352</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.006895948329105633</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer đầy đủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>geant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>rl_sac</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
         <v>0.7325171433055</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E9" t="n">
         <v>5.500397570221166</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F9" t="n">
         <v>0.4570151810587</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G9" t="n">
         <v>0.3049020189041333</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H9" t="n">
         <v>0.8636021459541947</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I9" t="n">
         <v>0.730455768133606</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J9" t="n">
         <v>0.009302896908573376</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K9" t="n">
         <v>0.03341606499940177</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L9" t="n">
         <v>0.006005831582476785</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M9" t="n">
         <v>0.000426434711520533</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N9" t="n">
         <v>0.001063443421572251</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O9" t="n">
         <v>0.02380732306626135</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>RL-Gate đầy đủ</t>
         </is>

--- a/results/gnn_rl_r2/bang_tong_hop_gnn_rl.xlsx
+++ b/results/gnn_rl_r2/bang_tong_hop_gnn_rl.xlsx
@@ -2416,7 +2416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2573,54 +2573,54 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>branch_odgraphformer</t>
+          <t>odgraphformer_no_route</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1.865058843375163</v>
+        <v>1.838791154538254</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70040789355798</v>
+        <v>16.67128153251738</v>
       </c>
       <c r="F3" t="n">
-        <v>1.290662242741793</v>
+        <v>1.276851711980588</v>
       </c>
       <c r="G3" t="n">
-        <v>1.127581840641289</v>
+        <v>1.111632992988715</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6631610039916939</v>
+        <v>0.6595016766479401</v>
       </c>
       <c r="I3" t="n">
-        <v>0.693999258952063</v>
+        <v>0.6961585334033337</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03854304387669896</v>
+        <v>0.02486354547555956</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1517201073215417</v>
+        <v>0.06172392394968123</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03391171549111292</v>
+        <v>0.02518469633864192</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02175481585310571</v>
+        <v>0.01556506138003693</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002655634846744731</v>
+        <v>0.002822942138749441</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01004087190073974</v>
+        <v>0.009195467297945115</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>OD-GraphFormer đầy đủ</t>
+          <t>OD-GraphFormer: bỏ A_route</t>
         </is>
       </c>
     </row>
@@ -2632,288 +2632,819 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rl_sac</t>
+          <t>odgraphformer_no_spatial_attn</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.741927542336333</v>
+        <v>1.831060802697169</v>
       </c>
       <c r="E4" t="n">
-        <v>16.11773536284043</v>
+        <v>16.64862678983163</v>
       </c>
       <c r="F4" t="n">
-        <v>1.219515474169</v>
+        <v>1.291143825301902</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9903039665075666</v>
+        <v>1.099679586894333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6732057282493242</v>
+        <v>0.6598058856433145</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6914339562174563</v>
+        <v>0.684185973417304</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02799032610468896</v>
+        <v>0.02557304186502911</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01936921920168383</v>
+        <v>0.09439355200199924</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03162539616048825</v>
+        <v>0.02725242253345186</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002286768080839772</v>
+        <v>0.01538773306268984</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00548953849602035</v>
+        <v>0.003210288825657157</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01885965186832127</v>
+        <v>0.01309859779085454</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>RL-Gate đầy đủ</t>
+          <t>OD-GraphFormer: bỏ attention giữa luồng</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>abilene</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>odgraphformer_anchor_other</t>
+          <t>rl_sac_no_gnn</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.241671820979177</v>
+        <v>1.723242758875166</v>
       </c>
       <c r="E5" t="n">
-        <v>46.91075294655811</v>
+        <v>16.11862418299667</v>
       </c>
       <c r="F5" t="n">
-        <v>6.15307807173128</v>
+        <v>1.187511093518967</v>
       </c>
       <c r="G5" t="n">
-        <v>6.103424738772945</v>
+        <v>0.9999490964426999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2775064123105972</v>
+        <v>0.6687155084269653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5073088904665698</v>
+        <v>0.7153522625052275</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06546515712493083</v>
+        <v>0.02398410805924425</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4886559151486015</v>
+        <v>0.02414844282927352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06659622812768393</v>
+        <v>0.02689055419263298</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06049385053986069</v>
+        <v>0.004977890763077962</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0007622432105073889</v>
+        <v>0.004322743127044561</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0004097420982194802</v>
+        <v>0.01655735132734033</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>OD-GraphFormer: đổi mốc neo</t>
+          <t>RL-Gate: bỏ GNN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>abilene</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rl_sac_no_gnn</t>
+          <t>rl_sac_no_oof</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2.526884055769033</v>
+        <v>1.757629096662833</v>
       </c>
       <c r="E6" t="n">
-        <v>30.6373840840146</v>
+        <v>16.13326242802593</v>
       </c>
       <c r="F6" t="n">
-        <v>2.446282949405433</v>
+        <v>1.236227326968833</v>
       </c>
       <c r="G6" t="n">
-        <v>2.445795380431734</v>
+        <v>0.9935106176456999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3045464364137818</v>
+        <v>0.6756664189474758</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5915783431562126</v>
+        <v>0.6836838345971991</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01171836874170525</v>
+        <v>0.02587629337485644</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1018005994236661</v>
+        <v>0.01734407068427491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006158558605112071</v>
+        <v>0.02798139089941025</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006527990504429688</v>
+        <v>0.003853303248199733</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004780548717228087</v>
+        <v>0.004732542926931086</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008173145829810961</v>
+        <v>0.0143507294570102</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>RL-Gate: bỏ GNN</t>
+          <t>RL-Gate: không dùng OOF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>abilene</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>branch_odgraphformer</t>
+          <t>rl_sac_static_prior</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3.275939339445269</v>
+        <v>1.854921971300267</v>
       </c>
       <c r="E7" t="n">
-        <v>33.40333384770963</v>
+        <v>16.27630254250787</v>
       </c>
       <c r="F7" t="n">
-        <v>3.198150901368716</v>
+        <v>1.3323761567994</v>
       </c>
       <c r="G7" t="n">
-        <v>3.200922308007646</v>
+        <v>1.019034720511633</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3680763344595437</v>
+        <v>0.6871618383586869</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5221657645026699</v>
+        <v>0.6447362739105413</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02445585208043611</v>
+        <v>0.006979912727389748</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09788571096086617</v>
+        <v>0.01283185425646117</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02001141852785259</v>
+        <v>0.006266781510627446</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02216506221139106</v>
+        <v>0.005474656894327247</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002837019573262881</v>
+        <v>0.0009261202514247068</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005613294760228453</v>
+        <v>0.00291673953238383</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>OD-GraphFormer đầy đủ</t>
+          <t>RL-Gate: prior tĩnh thay cho Hedge</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>branch_odgraphformer</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.865058843375163</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16.70040789355798</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.290662242741793</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.127581840641289</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6631610039916939</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.693999258952063</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.03854304387669896</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1517201073215417</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.03391171549111292</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.02175481585310571</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002655634846744731</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01004087190073974</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer đầy đủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.741927542336333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.11773536284043</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.219515474169</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9903039665075666</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6732057282493242</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.6914339562174563</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02799032610468896</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01936921920168383</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03162539616048825</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.002286768080839772</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00548953849602035</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01885965186832127</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>RL-Gate đầy đủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>sdn</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>odgraphformer_anchor_other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.90363033856302</v>
+      </c>
+      <c r="E10" t="n">
+        <v>48.91768632306667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.812225729253215</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.740752226991248</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2771339762132631</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5076099441262759</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.147479882352668</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.493241622753426</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.142647991312451</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.104712059630257</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0008406148319977808</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005965267903406159</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer: đổi mốc neo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>odgraphformer_no_route</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.288097649794141</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33.50458127150667</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.2094027979253</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.208828860752834</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3689557696939614</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.532622246355558</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.02267320709251402</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1542218980341593</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01966759154997015</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02018401763747529</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.003951491336967723</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.003406916330848027</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer: bỏ A_route</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>odgraphformer_no_spatial_attn</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.390349660355507</v>
+      </c>
+      <c r="E12" t="n">
+        <v>33.97202682074374</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.31082557164834</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.313831510798346</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3678399670571994</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5119505309159859</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.04025947870514123</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1441058467849993</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0434801893588834</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.04209869626606313</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.004239977708367532</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.009521616929400236</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer: bỏ attention giữa luồng</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rl_sac_no_gnn</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.526884055769033</v>
+      </c>
+      <c r="E13" t="n">
+        <v>30.6373840840146</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.446282949405433</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.445795380431734</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3045464364137818</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5915783431562126</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.01171836874170525</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1018005994236661</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.006158558605112071</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.006527990504429688</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.004780548717228087</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.008173145829810961</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>RL-Gate: bỏ GNN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>rl_sac_no_oof</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.5497335525478</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30.90072044499893</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.46173437722</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.463699584276067</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3011439407912123</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5972459504201276</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.01951020500544375</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2022885746845685</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.01711590849733897</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0147330783468372</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.002246024549034996</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01042443915952839</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>RL-Gate: không dùng OOF</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rl_sac_static_prior</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.4633055301639</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30.22431248460627</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.3828576285307</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.384830539811467</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3062464200082399</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6022196947349419</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.02843417963963295</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2447208420195335</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.02662003528902661</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.02785401456964875</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.005885670347147627</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.008632083428722652</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>RL-Gate: prior tĩnh thay cho Hedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>branch_odgraphformer</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.275939339445269</v>
+      </c>
+      <c r="E16" t="n">
+        <v>33.40333384770963</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.198150901368716</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.200922308007646</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3680763344595437</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5221657645026699</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.02445585208043611</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.09788571096086617</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.02001141852785259</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.02216506221139106</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.002837019573262881</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.005613294760228453</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer đầy đủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>rl_sac</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
         <v>2.508581521084567</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E17" t="n">
         <v>30.49988902130983</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F17" t="n">
         <v>2.419073475473233</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G17" t="n">
         <v>2.4216139395647</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H17" t="n">
         <v>0.3058066576401515</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I17" t="n">
         <v>0.6268345429648211</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J17" t="n">
         <v>0.01824697419980081</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K17" t="n">
         <v>0.09032365015530926</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L17" t="n">
         <v>0.01513926132260117</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M17" t="n">
         <v>0.01480403704306503</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N17" t="n">
         <v>0.00603085734927045</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O17" t="n">
         <v>0.02224755347815674</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>RL-Gate đầy đủ</t>
         </is>

--- a/results/gnn_rl_r2/bang_tong_hop_gnn_rl.xlsx
+++ b/results/gnn_rl_r2/bang_tong_hop_gnn_rl.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,7 +1464,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1476,22 +1476,22 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26.55449157545777</v>
+        <v>0.8545949154731397</v>
       </c>
       <c r="E18" t="n">
-        <v>90.96799341654842</v>
+        <v>5.632607437995413</v>
       </c>
       <c r="F18" t="n">
-        <v>26.42186862643311</v>
+        <v>0.5819590981680846</v>
       </c>
       <c r="G18" t="n">
-        <v>25.69528161983637</v>
+        <v>0.339302939314644</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2110912108471329</v>
+        <v>0.8691391710779487</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4498484483944032</v>
+        <v>0.5329569135522744</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1535,40 +1535,40 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>5.501746132110231</v>
+        <v>0.9160362802011897</v>
       </c>
       <c r="E19" t="n">
-        <v>43.50135691079012</v>
+        <v>5.864958530080304</v>
       </c>
       <c r="F19" t="n">
-        <v>5.400941108775661</v>
+        <v>0.4552296270502245</v>
       </c>
       <c r="G19" t="n">
-        <v>5.38897000852714</v>
+        <v>0.3443731357643805</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3104524120407648</v>
+        <v>0.8797340421617648</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5979225042188075</v>
+        <v>0.7289891544548174</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03648634416566095</v>
+        <v>0.001991306910794514</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1800025294142001</v>
+        <v>0.003753233538075241</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03583735584964644</v>
+        <v>0.000699093897774393</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03555507731483454</v>
+        <v>0.0006337084715600187</v>
       </c>
       <c r="N19" t="n">
-        <v>0.002514829252129105</v>
+        <v>0.0004551147754948264</v>
       </c>
       <c r="O19" t="n">
-        <v>0.008006618946304844</v>
+        <v>0.0004809586111362458</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1582,7 +1582,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1594,40 +1594,40 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>4.725293687942619</v>
+        <v>0.7511689919265434</v>
       </c>
       <c r="E20" t="n">
-        <v>40.09050711039001</v>
+        <v>5.755513447990891</v>
       </c>
       <c r="F20" t="n">
-        <v>4.622366665383944</v>
+        <v>0.4643777229002375</v>
       </c>
       <c r="G20" t="n">
-        <v>4.58088827254178</v>
+        <v>0.3101534872891977</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3346154045021904</v>
+        <v>0.863424599693689</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5685760891694658</v>
+        <v>0.7024949865466629</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04001095344222513</v>
+        <v>0.0007415452738515091</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2356779729660841</v>
+        <v>0.006526737487821046</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04040968708202303</v>
+        <v>0.0009672950477639932</v>
       </c>
       <c r="M20" t="n">
-        <v>0.04102459753013328</v>
+        <v>0.0005450964630930178</v>
       </c>
       <c r="N20" t="n">
-        <v>0.002412511766822248</v>
+        <v>0.000335233721423481</v>
       </c>
       <c r="O20" t="n">
-        <v>0.003194804001046742</v>
+        <v>0.00137040939017097</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -1641,7 +1641,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1653,40 +1653,40 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>15.05727505024088</v>
+        <v>0.7362113194966695</v>
       </c>
       <c r="E21" t="n">
-        <v>64.31187253033912</v>
+        <v>5.399883671026634</v>
       </c>
       <c r="F21" t="n">
-        <v>14.95331586609725</v>
+        <v>0.4686869846584136</v>
       </c>
       <c r="G21" t="n">
-        <v>14.62828864718621</v>
+        <v>0.325092830932584</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3033576975106618</v>
+        <v>0.8610793040993343</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7939136373143997</v>
+        <v>0.7934766876314812</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3879300898569781</v>
+        <v>0.007013931251638423</v>
       </c>
       <c r="K21" t="n">
-        <v>1.442674289781311</v>
+        <v>0.009629990920579486</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3902316522193149</v>
+        <v>0.001906264768356159</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3791228986791557</v>
+        <v>0.002963214704868111</v>
       </c>
       <c r="N21" t="n">
-        <v>0.007868257797702578</v>
+        <v>0.002152269993402452</v>
       </c>
       <c r="O21" t="n">
-        <v>0.006935287930042821</v>
+        <v>0.004500665234824578</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1712,43 +1712,43 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>3.275939339445269</v>
+        <v>0.768482934427742</v>
       </c>
       <c r="E22" t="n">
-        <v>33.40333384770963</v>
+        <v>5.7123537593092</v>
       </c>
       <c r="F22" t="n">
-        <v>3.198150901368716</v>
+        <v>0.5024813722540648</v>
       </c>
       <c r="G22" t="n">
-        <v>3.200922308007646</v>
+        <v>0.3086315974355888</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3680763344595437</v>
+        <v>0.8675420811647035</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5221657645026699</v>
+        <v>0.6516442537487873</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02445585208043611</v>
+        <v>0.008202309350803816</v>
       </c>
       <c r="K22" t="n">
-        <v>0.09788571096086617</v>
+        <v>0.03383439908779904</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02001141852785259</v>
+        <v>0.005420806961698338</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02216506221139106</v>
+        <v>0.003168122195565833</v>
       </c>
       <c r="N22" t="n">
-        <v>0.002837019573262881</v>
+        <v>0.001108314726900352</v>
       </c>
       <c r="O22" t="n">
-        <v>0.005613294760228453</v>
+        <v>0.006895948329105633</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1771,40 +1771,40 @@
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>4.016685571412967</v>
+        <v>0.7235077901182334</v>
       </c>
       <c r="E23" t="n">
-        <v>38.12959362032276</v>
+        <v>5.456814616815633</v>
       </c>
       <c r="F23" t="n">
-        <v>3.9141140577925</v>
+        <v>0.4468465863660333</v>
       </c>
       <c r="G23" t="n">
-        <v>3.881554694383667</v>
+        <v>0.3137544199187</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3216286447809846</v>
+        <v>0.8614537406438583</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6358823934634544</v>
+        <v>0.8109079800947187</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0511924947251717</v>
+        <v>0.005211460970558278</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2919558767863844</v>
+        <v>0.03228928404691184</v>
       </c>
       <c r="L23" t="n">
-        <v>0.05138622364983586</v>
+        <v>0.0001647485566469421</v>
       </c>
       <c r="M23" t="n">
-        <v>0.05120899677502607</v>
+        <v>0.0007953819053387523</v>
       </c>
       <c r="N23" t="n">
-        <v>0.002258133129645119</v>
+        <v>0.001500156802479793</v>
       </c>
       <c r="O23" t="n">
-        <v>0.002740557556229231</v>
+        <v>0.0003630989720368629</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1830,43 +1830,43 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>3.9476626848196</v>
+        <v>0.7509228419623</v>
       </c>
       <c r="E24" t="n">
-        <v>37.6526229201889</v>
+        <v>5.476798346813034</v>
       </c>
       <c r="F24" t="n">
-        <v>3.845159317517933</v>
+        <v>0.4530580877056</v>
       </c>
       <c r="G24" t="n">
-        <v>3.830410363113133</v>
+        <v>0.3096083411554667</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3222551732681814</v>
+        <v>0.8667797936269444</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6448272323192081</v>
+        <v>0.7498925388309371</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03882123165549818</v>
+        <v>0.006005242976661457</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2017558915765555</v>
+        <v>0.02169424186709799</v>
       </c>
       <c r="L24" t="n">
-        <v>0.03889882315486708</v>
+        <v>0.002751834581347446</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03762575477558885</v>
+        <v>0.0001239592477014685</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0005513806864590499</v>
+        <v>0.001177477388476133</v>
       </c>
       <c r="O24" t="n">
-        <v>0.00207302644819922</v>
+        <v>0.005477743008194503</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1889,43 +1889,43 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>3.9476626848196</v>
+        <v>0.7319333039489667</v>
       </c>
       <c r="E25" t="n">
-        <v>37.6526229201889</v>
+        <v>5.460561685895634</v>
       </c>
       <c r="F25" t="n">
-        <v>3.845159317517933</v>
+        <v>0.4492073492143667</v>
       </c>
       <c r="G25" t="n">
-        <v>3.830410363113133</v>
+        <v>0.3092456947267667</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3222551732681814</v>
+        <v>0.8636356905413566</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6448272323192081</v>
+        <v>0.7792757589332084</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03882123165549818</v>
+        <v>0.008363045559222064</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2017558915765555</v>
+        <v>0.0277983244997138</v>
       </c>
       <c r="L25" t="n">
-        <v>0.03889882315486708</v>
+        <v>0.00312871381477208</v>
       </c>
       <c r="M25" t="n">
-        <v>0.03762575477558885</v>
+        <v>0.000152946769069385</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0005513806864590499</v>
+        <v>0.001281466853810315</v>
       </c>
       <c r="O25" t="n">
-        <v>0.00207302644819922</v>
+        <v>0.01234249256018032</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1948,40 +1948,40 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2.478177088888334</v>
+        <v>0.7233875943228</v>
       </c>
       <c r="E26" t="n">
-        <v>30.69257856951146</v>
+        <v>5.456793299060534</v>
       </c>
       <c r="F26" t="n">
-        <v>2.394402941809133</v>
+        <v>0.4468773058123</v>
       </c>
       <c r="G26" t="n">
-        <v>2.394136380959734</v>
+        <v>0.3136875631909999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2950405430867678</v>
+        <v>0.8614385429715385</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6012046888871669</v>
+        <v>0.8108008723286072</v>
       </c>
       <c r="J26" t="n">
-        <v>0.01250518137547089</v>
+        <v>0.005204797441529852</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1536628387075126</v>
+        <v>0.03237072433826701</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01335667753528763</v>
+        <v>0.0001748592298297783</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01220553402859052</v>
+        <v>0.0007838972503910924</v>
       </c>
       <c r="N26" t="n">
-        <v>0.004501408379309078</v>
+        <v>0.001497944495851466</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00983866041475477</v>
+        <v>0.0003534992493137711</v>
       </c>
       <c r="P26" t="n">
         <v>3</v>
@@ -1995,7 +1995,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2007,43 +2007,43 @@
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2.456527837997767</v>
+        <v>0.7466946056113</v>
       </c>
       <c r="E27" t="n">
-        <v>30.3779610552362</v>
+        <v>5.482472803001467</v>
       </c>
       <c r="F27" t="n">
-        <v>2.369377524736733</v>
+        <v>0.4637493550774667</v>
       </c>
       <c r="G27" t="n">
-        <v>2.370364045085033</v>
+        <v>0.3057206956276333</v>
       </c>
       <c r="H27" t="n">
-        <v>0.299489802149374</v>
+        <v>0.8660964321152959</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6030320569817853</v>
+        <v>0.7052791258854744</v>
       </c>
       <c r="J27" t="n">
-        <v>0.01153749974998899</v>
+        <v>0.006792393775585804</v>
       </c>
       <c r="K27" t="n">
-        <v>0.07055102979094806</v>
+        <v>0.02734195474748616</v>
       </c>
       <c r="L27" t="n">
-        <v>0.008363154909082812</v>
+        <v>0.00428701541763646</v>
       </c>
       <c r="M27" t="n">
-        <v>0.01040668296028715</v>
+        <v>0.0001308174887047891</v>
       </c>
       <c r="N27" t="n">
-        <v>0.002796721633493056</v>
+        <v>0.001224808183458965</v>
       </c>
       <c r="O27" t="n">
-        <v>0.00977054207532801</v>
+        <v>0.005632193152188633</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2066,43 +2066,43 @@
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>2.456527837997767</v>
+        <v>0.7238078657059334</v>
       </c>
       <c r="E28" t="n">
-        <v>30.3779610552362</v>
+        <v>5.460704995547166</v>
       </c>
       <c r="F28" t="n">
-        <v>2.369377524736733</v>
+        <v>0.4547109559629333</v>
       </c>
       <c r="G28" t="n">
-        <v>2.370364045085033</v>
+        <v>0.3055258151943667</v>
       </c>
       <c r="H28" t="n">
-        <v>0.299489802149374</v>
+        <v>0.8622627962041195</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6030320569817853</v>
+        <v>0.7541161025560007</v>
       </c>
       <c r="J28" t="n">
-        <v>0.01153749974998899</v>
+        <v>0.007883250640196073</v>
       </c>
       <c r="K28" t="n">
-        <v>0.07055102979094806</v>
+        <v>0.03348926003715503</v>
       </c>
       <c r="L28" t="n">
-        <v>0.008363154909082812</v>
+        <v>0.005367584868093273</v>
       </c>
       <c r="M28" t="n">
-        <v>0.01040668296028715</v>
+        <v>0.0007827677499348093</v>
       </c>
       <c r="N28" t="n">
-        <v>0.002796721633493056</v>
+        <v>0.001148211407191679</v>
       </c>
       <c r="O28" t="n">
-        <v>0.00977054207532801</v>
+        <v>0.01969743768694179</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2125,43 +2125,43 @@
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2.456527837997767</v>
+        <v>0.7319933864281666</v>
       </c>
       <c r="E29" t="n">
-        <v>30.3779610552362</v>
+        <v>5.471714450709032</v>
       </c>
       <c r="F29" t="n">
-        <v>2.369377524736733</v>
+        <v>0.4570650690030333</v>
       </c>
       <c r="G29" t="n">
-        <v>2.370364045085033</v>
+        <v>0.3055050140911333</v>
       </c>
       <c r="H29" t="n">
-        <v>0.299489802149374</v>
+        <v>0.8636181790655167</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6030320569817853</v>
+        <v>0.7338829864310928</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01153749974998899</v>
+        <v>0.00999474194871945</v>
       </c>
       <c r="K29" t="n">
-        <v>0.07055102979094806</v>
+        <v>0.03696861353679547</v>
       </c>
       <c r="L29" t="n">
-        <v>0.008363154909082812</v>
+        <v>0.006030338317335833</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01040668296028715</v>
+        <v>0.0002303593824121076</v>
       </c>
       <c r="N29" t="n">
-        <v>0.002796721633493056</v>
+        <v>0.001165712069095314</v>
       </c>
       <c r="O29" t="n">
-        <v>0.00977054207532801</v>
+        <v>0.02637785850382522</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2184,43 +2184,43 @@
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>3.0879648935226</v>
+        <v>0.8349365125913333</v>
       </c>
       <c r="E30" t="n">
-        <v>32.25693200589996</v>
+        <v>5.479456565965866</v>
       </c>
       <c r="F30" t="n">
-        <v>3.0040905373175</v>
+        <v>0.4420127685105</v>
       </c>
       <c r="G30" t="n">
-        <v>3.002657700765567</v>
+        <v>0.3174623745941667</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3761958157878631</v>
+        <v>0.8792173827468303</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5317360325350564</v>
+        <v>0.7454271966902367</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00897752237096593</v>
+        <v>0.01364091102173445</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05608994541375536</v>
+        <v>0.03353881760974679</v>
       </c>
       <c r="L30" t="n">
-        <v>0.005812948580429253</v>
+        <v>0.0005532770688356091</v>
       </c>
       <c r="M30" t="n">
-        <v>0.007503583587284229</v>
+        <v>0.000415178436094045</v>
       </c>
       <c r="N30" t="n">
-        <v>0.001400160197770677</v>
+        <v>0.001235894984593502</v>
       </c>
       <c r="O30" t="n">
-        <v>0.004605794822761412</v>
+        <v>0.007534088560884071</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2243,43 +2243,43 @@
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>2.3989559454172</v>
+        <v>0.7806467503629666</v>
       </c>
       <c r="E31" t="n">
-        <v>29.90448607110877</v>
+        <v>5.496599564288402</v>
       </c>
       <c r="F31" t="n">
-        <v>2.308984261640566</v>
+        <v>0.443644442543</v>
       </c>
       <c r="G31" t="n">
-        <v>2.3093347317303</v>
+        <v>0.3109670056512</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3058531896451391</v>
+        <v>0.8717143095172925</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6062370821860633</v>
+        <v>0.752236669343834</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01538733195301602</v>
+        <v>0.03152990814516696</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1712956753732364</v>
+        <v>0.03067359814998565</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01938751010307544</v>
+        <v>0.01595094301828193</v>
       </c>
       <c r="M31" t="n">
-        <v>0.01693498275440689</v>
+        <v>0.002901415405026757</v>
       </c>
       <c r="N31" t="n">
-        <v>0.002505677633406062</v>
+        <v>0.005832843230684426</v>
       </c>
       <c r="O31" t="n">
-        <v>0.008900703373289218</v>
+        <v>0.04164062220232631</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2302,43 +2302,43 @@
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7325171433055</v>
       </c>
       <c r="E32" t="n">
-        <v>30.49988902130983</v>
+        <v>5.500397570221166</v>
       </c>
       <c r="F32" t="n">
-        <v>2.419073475473233</v>
+        <v>0.4570151810587</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4216139395647</v>
+        <v>0.3049020189041333</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3058066576401515</v>
+        <v>0.8636021459541947</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6268345429648211</v>
+        <v>0.730455768133606</v>
       </c>
       <c r="J32" t="n">
-        <v>0.01824697419980081</v>
+        <v>0.009302896908573376</v>
       </c>
       <c r="K32" t="n">
-        <v>0.09032365015530926</v>
+        <v>0.03341606499940177</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01513926132260117</v>
+        <v>0.006005831582476785</v>
       </c>
       <c r="M32" t="n">
-        <v>0.01480403704306503</v>
+        <v>0.000426434711520533</v>
       </c>
       <c r="N32" t="n">
-        <v>0.00603085734927045</v>
+        <v>0.001063443421572251</v>
       </c>
       <c r="O32" t="n">
-        <v>0.02224755347815674</v>
+        <v>0.02380732306626135</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2349,57 +2349,1001 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>geant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.7319933864281666</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.471714450709032</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.4570650690030333</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.3055050140911333</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8636181790655167</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7338829864310928</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.00999474194871945</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.03696861353679547</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.006030338317335833</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.0002303593824121076</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.001165712069095314</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.02637785850382522</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>ST-Adaptive-Ensemble-RL</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>sdn</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>persistence</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>26.55449157545777</v>
+      </c>
+      <c r="E34" t="n">
+        <v>90.96799341654842</v>
+      </c>
+      <c r="F34" t="n">
+        <v>26.42186862643311</v>
+      </c>
+      <c r="G34" t="n">
+        <v>25.69528161983637</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2110912108471329</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4498484483944032</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>branch_xgboost</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5.501746132110231</v>
+      </c>
+      <c r="E35" t="n">
+        <v>43.50135691079012</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.400941108775661</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.38897000852714</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3104524120407648</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5979225042188075</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.03648634416566095</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.1800025294142001</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.03583735584964644</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.03555507731483454</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.002514829252129105</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.008006618946304844</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>branch_lightgbm_res</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4.725293687942619</v>
+      </c>
+      <c r="E36" t="n">
+        <v>40.09050711039001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.622366665383944</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.58088827254178</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3346154045021904</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5685760891694658</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.04001095344222513</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.2356779729660841</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.04040968708202303</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.04102459753013328</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.002412511766822248</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.003194804001046742</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>LightGBM-Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>branch_stwaveformer</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.05727505024088</v>
+      </c>
+      <c r="E37" t="n">
+        <v>64.31187253033912</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14.95331586609725</v>
+      </c>
+      <c r="G37" t="n">
+        <v>14.62828864718621</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3033576975106618</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7939136373143997</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.3879300898569781</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.442674289781311</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.3902316522193149</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.3791228986791557</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.007868257797702578</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.006935287930042821</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>ST-WaveFormer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>branch_odgraphformer</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.275939339445269</v>
+      </c>
+      <c r="E38" t="n">
+        <v>33.40333384770963</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.198150901368716</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.200922308007646</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3680763344595437</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.5221657645026699</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.02445585208043611</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.09788571096086617</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.02001141852785259</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.02216506221139106</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.002837019573262881</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.005613294760228453</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>v3_static</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4.016685571412967</v>
+      </c>
+      <c r="E39" t="n">
+        <v>38.12959362032276</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.9141140577925</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.881554694383667</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3216286447809846</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.6358823934634544</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0511924947251717</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.2919558767863844</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.05138622364983586</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.05120899677502607</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.002258133129645119</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.002740557556229231</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>ST-Adaptive-Ensemble v3 (static)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>hedge_v3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.9476626848196</v>
+      </c>
+      <c r="E40" t="n">
+        <v>37.6526229201889</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.845159317517933</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.830410363113133</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3222551732681814</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6448272323192081</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.03882123165549818</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.2017558915765555</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.03889882315486708</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.03762575477558885</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.0005513806864590499</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.00207302644819922</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Hedge (3 nhánh v3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>hedge_floor_v3</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.9476626848196</v>
+      </c>
+      <c r="E41" t="n">
+        <v>37.6526229201889</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.845159317517933</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.830410363113133</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3222551732681814</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6448272323192081</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.03882123165549818</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.2017558915765555</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.03889882315486708</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.03762575477558885</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.0005513806864590499</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.00207302644819922</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Hedge + sàn (3 nhánh v3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>static_k4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.478177088888334</v>
+      </c>
+      <c r="E42" t="n">
+        <v>30.69257856951146</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.394402941809133</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.394136380959734</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2950405430867678</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6012046888871669</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.01250518137547089</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.1536628387075126</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.01335667753528763</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.01220553402859052</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.004501408379309078</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.00983866041475477</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Static K=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>hedge</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.456527837997767</v>
+      </c>
+      <c r="E43" t="n">
+        <v>30.3779610552362</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.369377524736733</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.370364045085033</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.299489802149374</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6030320569817853</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.01153749974998899</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.07055102979094806</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.008363154909082812</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.01040668296028715</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.002796721633493056</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.00977054207532801</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Hedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>hedge_floor</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.456527837997767</v>
+      </c>
+      <c r="E44" t="n">
+        <v>30.3779610552362</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.369377524736733</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.370364045085033</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.299489802149374</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.6030320569817853</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.01153749974998899</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.07055102979094806</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.008363154909082812</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.01040668296028715</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.002796721633493056</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.00977054207532801</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Hedge + sàn</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hedge_prior</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.456527837997767</v>
+      </c>
+      <c r="E45" t="n">
+        <v>30.3779610552362</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.369377524736733</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.370364045085033</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.299489802149374</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6030320569817853</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.01153749974998899</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.07055102979094806</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.008363154909082812</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.01040668296028715</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.002796721633493056</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.00977054207532801</v>
+      </c>
+      <c r="P45" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Prior Hedge + sàn (Huber)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>context_gate</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3.0879648935226</v>
+      </c>
+      <c r="E46" t="n">
+        <v>32.25693200589996</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.0040905373175</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.002657700765567</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.3761958157878631</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.5317360325350564</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.00897752237096593</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.05608994541375536</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.005812948580429253</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.007503583587284229</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.001400160197770677</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.004605794822761412</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Cổng MLP ngữ cảnh v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>rl_sup</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.3989559454172</v>
+      </c>
+      <c r="E47" t="n">
+        <v>29.90448607110877</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.308984261640566</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.3093347317303</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.3058531896451391</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.6062370821860633</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.01538733195301602</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.1712956753732364</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.01938751010307544</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.01693498275440689</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.002505677633406062</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.008900703373289218</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Gate giám sát (γ=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.508581521084567</v>
+      </c>
+      <c r="E48" t="n">
+        <v>30.49988902130983</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.419073475473233</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.4216139395647</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3058066576401515</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.6268345429648211</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.01824697419980081</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.09032365015530926</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.01513926132260117</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.01480403704306503</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.00603085734927045</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.02224755347815674</v>
+      </c>
+      <c r="P48" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>RL-Gate (SAC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>final</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
         <v>2.508581521084567</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E49" t="n">
         <v>30.49988902130983</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F49" t="n">
         <v>2.419073475473233</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G49" t="n">
         <v>2.4216139395647</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H49" t="n">
         <v>0.3058066576401515</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I49" t="n">
         <v>0.6268345429648211</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J49" t="n">
         <v>0.01824697419980081</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K49" t="n">
         <v>0.09032365015530926</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L49" t="n">
         <v>0.01513926132260117</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M49" t="n">
         <v>0.01480403704306503</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N49" t="n">
         <v>0.00603085734927045</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O49" t="n">
         <v>0.02224755347815674</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q33" t="inlineStr">
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>ST-Adaptive-Ensemble-RL</t>
         </is>
@@ -2416,7 +3360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2981,7 +3925,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2993,40 +3937,40 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>6.90363033856302</v>
+        <v>0.8529599437648349</v>
       </c>
       <c r="E10" t="n">
-        <v>48.91768632306667</v>
+        <v>6.451696177177171</v>
       </c>
       <c r="F10" t="n">
-        <v>6.812225729253215</v>
+        <v>0.5303602138375715</v>
       </c>
       <c r="G10" t="n">
-        <v>6.740752226991248</v>
+        <v>0.4105815077009556</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2771339762132631</v>
+        <v>0.8410626379657167</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5076099441262759</v>
+        <v>0.788967056594208</v>
       </c>
       <c r="J10" t="n">
-        <v>1.147479882352668</v>
+        <v>0.06048592013518149</v>
       </c>
       <c r="K10" t="n">
-        <v>3.493241622753426</v>
+        <v>0.2206744266692426</v>
       </c>
       <c r="L10" t="n">
-        <v>1.142647991312451</v>
+        <v>0.02404329681319459</v>
       </c>
       <c r="M10" t="n">
-        <v>1.104712059630257</v>
+        <v>0.04068560611319959</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0008406148319977808</v>
+        <v>0.01484813527176725</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0005965267903406159</v>
+        <v>0.02201287137563622</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3040,7 +3984,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3052,40 +3996,40 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3.288097649794141</v>
+        <v>0.7686703734414507</v>
       </c>
       <c r="E11" t="n">
-        <v>33.50458127150667</v>
+        <v>5.67993315733017</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2094027979253</v>
+        <v>0.5035612833228763</v>
       </c>
       <c r="G11" t="n">
-        <v>3.208828860752834</v>
+        <v>0.3095701677883538</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3689557696939614</v>
+        <v>0.867464381300552</v>
       </c>
       <c r="I11" t="n">
-        <v>0.532622246355558</v>
+        <v>0.6525396772918531</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02267320709251402</v>
+        <v>0.003272111058181306</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1542218980341593</v>
+        <v>0.03035039641455637</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01966759154997015</v>
+        <v>0.00180111570498093</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02018401763747529</v>
+        <v>0.001525134877253056</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003951491336967723</v>
+        <v>0.00163281332718471</v>
       </c>
       <c r="O11" t="n">
-        <v>0.003406916330848027</v>
+        <v>0.005698992196499716</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -3099,7 +4043,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3111,40 +4055,40 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3.390349660355507</v>
+        <v>0.7627785243677492</v>
       </c>
       <c r="E12" t="n">
-        <v>33.97202682074374</v>
+        <v>5.640104853273177</v>
       </c>
       <c r="F12" t="n">
-        <v>3.31082557164834</v>
+        <v>0.5004207742029969</v>
       </c>
       <c r="G12" t="n">
-        <v>3.313831510798346</v>
+        <v>0.3080711544997622</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3678399670571994</v>
+        <v>0.8667205244170576</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5119505309159859</v>
+        <v>0.6514559222601297</v>
       </c>
       <c r="J12" t="n">
-        <v>0.04025947870514123</v>
+        <v>0.0008169903622961447</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1441058467849993</v>
+        <v>0.07015797200121543</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0434801893588834</v>
+        <v>0.00136016738890838</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04209869626606313</v>
+        <v>0.001468826576874904</v>
       </c>
       <c r="N12" t="n">
-        <v>0.004239977708367532</v>
+        <v>0.0001608426202975126</v>
       </c>
       <c r="O12" t="n">
-        <v>0.009521616929400236</v>
+        <v>0.002947902353554886</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -3158,7 +4102,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3170,40 +4114,40 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2.526884055769033</v>
+        <v>0.7324499461620667</v>
       </c>
       <c r="E13" t="n">
-        <v>30.6373840840146</v>
+        <v>5.468607495383799</v>
       </c>
       <c r="F13" t="n">
-        <v>2.446282949405433</v>
+        <v>0.4505609488202333</v>
       </c>
       <c r="G13" t="n">
-        <v>2.445795380431734</v>
+        <v>0.3095732268565</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3045464364137818</v>
+        <v>0.8637099737891488</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5915783431562126</v>
+        <v>0.7660097805206326</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01171836874170525</v>
+        <v>0.01508006654970827</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1018005994236661</v>
+        <v>0.02966135059418695</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006158558605112071</v>
+        <v>0.01038397132690988</v>
       </c>
       <c r="M13" t="n">
-        <v>0.006527990504429688</v>
+        <v>0.00286661210289679</v>
       </c>
       <c r="N13" t="n">
-        <v>0.004780548717228087</v>
+        <v>0.002113997212412626</v>
       </c>
       <c r="O13" t="n">
-        <v>0.008173145829810961</v>
+        <v>0.05203381006858283</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -3217,7 +4161,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3229,40 +4173,40 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5497335525478</v>
+        <v>0.7319508214811667</v>
       </c>
       <c r="E14" t="n">
-        <v>30.90072044499893</v>
+        <v>5.471675044616366</v>
       </c>
       <c r="F14" t="n">
-        <v>2.46173437722</v>
+        <v>0.4570341028517333</v>
       </c>
       <c r="G14" t="n">
-        <v>2.463699584276067</v>
+        <v>0.3053813118828</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3011439407912123</v>
+        <v>0.8636252817450375</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5972459504201276</v>
+        <v>0.7334137130735394</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01951020500544375</v>
+        <v>0.009982208343762662</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2022885746845685</v>
+        <v>0.03225818847532842</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01711590849733897</v>
+        <v>0.006068809907354892</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0147330783468372</v>
+        <v>0.0003484073481395493</v>
       </c>
       <c r="N14" t="n">
-        <v>0.002246024549034996</v>
+        <v>0.001181278707752452</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01042443915952839</v>
+        <v>0.02595054690469781</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -3276,7 +4220,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3288,40 +4232,40 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4633055301639</v>
+        <v>0.7223496481252334</v>
       </c>
       <c r="E15" t="n">
-        <v>30.22431248460627</v>
+        <v>5.454022071541599</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3828576285307</v>
+        <v>0.4469904437010334</v>
       </c>
       <c r="G15" t="n">
-        <v>2.384830539811467</v>
+        <v>0.3134659875636001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3062464200082399</v>
+        <v>0.8612394714952375</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6022196947349419</v>
+        <v>0.8102807460588579</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02843417963963295</v>
+        <v>0.004665156863395726</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2447208420195335</v>
+        <v>0.0354066058991332</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02662003528902661</v>
+        <v>0.0002751116433246551</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02785401456964875</v>
+        <v>0.000710104055692522</v>
       </c>
       <c r="N15" t="n">
-        <v>0.005885670347147627</v>
+        <v>0.001467909444345737</v>
       </c>
       <c r="O15" t="n">
-        <v>0.008632083428722652</v>
+        <v>0.0002584864829614626</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -3335,7 +4279,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3347,40 +4291,40 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>3.275939339445269</v>
+        <v>0.768482934427742</v>
       </c>
       <c r="E16" t="n">
-        <v>33.40333384770963</v>
+        <v>5.7123537593092</v>
       </c>
       <c r="F16" t="n">
-        <v>3.198150901368716</v>
+        <v>0.5024813722540648</v>
       </c>
       <c r="G16" t="n">
-        <v>3.200922308007646</v>
+        <v>0.3086315974355888</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3680763344595437</v>
+        <v>0.8675420811647035</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5221657645026699</v>
+        <v>0.6516442537487873</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02445585208043611</v>
+        <v>0.008202309350803816</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09788571096086617</v>
+        <v>0.03383439908779904</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02001141852785259</v>
+        <v>0.005420806961698338</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02216506221139106</v>
+        <v>0.003168122195565833</v>
       </c>
       <c r="N16" t="n">
-        <v>0.002837019573262881</v>
+        <v>0.001108314726900352</v>
       </c>
       <c r="O16" t="n">
-        <v>0.005613294760228453</v>
+        <v>0.006895948329105633</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -3394,57 +4338,529 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>geant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7325171433055</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5.500397570221166</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4570151810587</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3049020189041333</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8636021459541947</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.730455768133606</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.009302896908573376</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.03341606499940177</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.006005831582476785</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.000426434711520533</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.001063443421572251</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.02380732306626135</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>RL-Gate đầy đủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>sdn</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>odgraphformer_anchor_other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.90363033856302</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48.91768632306667</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.812225729253215</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.740752226991248</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2771339762132631</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5076099441262759</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.147479882352668</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.493241622753426</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.142647991312451</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.104712059630257</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.0008406148319977808</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0005965267903406159</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer: đổi mốc neo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>odgraphformer_no_route</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.288097649794141</v>
+      </c>
+      <c r="E19" t="n">
+        <v>33.50458127150667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.2094027979253</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.208828860752834</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3689557696939614</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.532622246355558</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.02267320709251402</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.1542218980341593</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.01966759154997015</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.02018401763747529</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.003951491336967723</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.003406916330848027</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer: bỏ A_route</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>odgraphformer_no_spatial_attn</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.390349660355507</v>
+      </c>
+      <c r="E20" t="n">
+        <v>33.97202682074374</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.31082557164834</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.313831510798346</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3678399670571994</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5119505309159859</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.04025947870514123</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1441058467849993</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0434801893588834</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.04209869626606313</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.004239977708367532</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.009521616929400236</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer: bỏ attention giữa luồng</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rl_sac_no_gnn</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.526884055769033</v>
+      </c>
+      <c r="E21" t="n">
+        <v>30.6373840840146</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.446282949405433</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.445795380431734</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3045464364137818</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5915783431562126</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.01171836874170525</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.1018005994236661</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.006158558605112071</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.006527990504429688</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.004780548717228087</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.008173145829810961</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>RL-Gate: bỏ GNN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rl_sac_no_oof</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.5497335525478</v>
+      </c>
+      <c r="E22" t="n">
+        <v>30.90072044499893</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.46173437722</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.463699584276067</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3011439407912123</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5972459504201276</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.01951020500544375</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2022885746845685</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.01711590849733897</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0147330783468372</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.002246024549034996</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.01042443915952839</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>RL-Gate: không dùng OOF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>rl_sac_static_prior</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.4633055301639</v>
+      </c>
+      <c r="E23" t="n">
+        <v>30.22431248460627</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.3828576285307</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.384830539811467</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3062464200082399</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6022196947349419</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.02843417963963295</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2447208420195335</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.02662003528902661</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.02785401456964875</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.005885670347147627</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.008632083428722652</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>RL-Gate: prior tĩnh thay cho Hedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>branch_odgraphformer</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.275939339445269</v>
+      </c>
+      <c r="E24" t="n">
+        <v>33.40333384770963</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.198150901368716</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.200922308007646</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3680763344595437</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5221657645026699</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.02445585208043611</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.09788571096086617</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.02001141852785259</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.02216506221139106</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.002837019573262881</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.005613294760228453</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>OD-GraphFormer đầy đủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>rl_sac</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
         <v>2.508581521084567</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E25" t="n">
         <v>30.49988902130983</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F25" t="n">
         <v>2.419073475473233</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G25" t="n">
         <v>2.4216139395647</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H25" t="n">
         <v>0.3058066576401515</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I25" t="n">
         <v>0.6268345429648211</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J25" t="n">
         <v>0.01824697419980081</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K25" t="n">
         <v>0.09032365015530926</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L25" t="n">
         <v>0.01513926132260117</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M25" t="n">
         <v>0.01480403704306503</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N25" t="n">
         <v>0.00603085734927045</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O25" t="n">
         <v>0.02224755347815674</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>RL-Gate đầy đủ</t>
         </is>
@@ -3461,7 +4877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3534,7 +4950,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3551,28 +4967,28 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7319933864281666</v>
       </c>
       <c r="F2" t="n">
-        <v>4.016685571412967</v>
+        <v>0.7235077901182333</v>
       </c>
       <c r="G2" t="n">
-        <v>-37.54598221632489</v>
+        <v>1.172841042740758</v>
       </c>
       <c r="H2" t="n">
-        <v>-39.30746520066631</v>
+        <v>1.031514645964431</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006465893522372362</v>
+        <v>0.4107095186427356</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>-39.40939128165797</v>
+        <v>0.4475330589267452</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -3581,7 +4997,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3598,28 +5014,28 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7319933864281666</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9476626848196</v>
+        <v>0.7509228419623</v>
       </c>
       <c r="G3" t="n">
-        <v>-36.45400528441544</v>
+        <v>-2.520825639644586</v>
       </c>
       <c r="H3" t="n">
-        <v>-44.95555630399251</v>
+        <v>-2.253945342577576</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004944371081306192</v>
+        <v>0.1529315960423807</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>-50.57693709663502</v>
+        <v>-0.6287700288979202</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -3628,7 +5044,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3645,37 +5061,37 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7319933864281666</v>
       </c>
       <c r="F4" t="n">
-        <v>2.478177088888334</v>
+        <v>0.7233875943228</v>
       </c>
       <c r="G4" t="n">
-        <v>1.226886986106068</v>
+        <v>1.189651602115593</v>
       </c>
       <c r="H4" t="n">
-        <v>1.714246157832544</v>
+        <v>1.0479400349275</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2286179923688734</v>
+        <v>0.4046350998373548</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.444055997274246</v>
+        <v>0.4562523877989839</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3692,28 +5108,28 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7325171433055</v>
       </c>
       <c r="F5" t="n">
-        <v>4.016685571412967</v>
+        <v>0.7235077901182333</v>
       </c>
       <c r="G5" t="n">
-        <v>-37.54598221632489</v>
+        <v>1.245232367960325</v>
       </c>
       <c r="H5" t="n">
-        <v>-39.30746520066631</v>
+        <v>1.15313561602845</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006465893522372362</v>
+        <v>0.3680591723140784</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>-39.40939128165797</v>
+        <v>0.4892211156439658</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -3722,7 +5138,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3739,28 +5155,28 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7325171433055</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9476626848196</v>
+        <v>0.7509228419623</v>
       </c>
       <c r="G6" t="n">
-        <v>-36.45400528441544</v>
+        <v>-2.451077211701613</v>
       </c>
       <c r="H6" t="n">
-        <v>-44.95555630399251</v>
+        <v>-2.30470164503692</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004944371081306192</v>
+        <v>0.1476714726098478</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>-50.57693709663502</v>
+        <v>-0.629998155312434</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -3769,7 +5185,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3786,37 +5202,37 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7325171433055</v>
       </c>
       <c r="F7" t="n">
-        <v>2.478177088888334</v>
+        <v>0.7233875943228</v>
       </c>
       <c r="G7" t="n">
-        <v>1.226886986106068</v>
+        <v>1.262054955648861</v>
       </c>
       <c r="H7" t="n">
-        <v>1.714246157832544</v>
+        <v>1.170653505162036</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2286179923688734</v>
+        <v>0.3623450464022745</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.444055997274246</v>
+        <v>0.4978145792919624</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3833,37 +5249,37 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7325171433055</v>
       </c>
       <c r="F8" t="n">
-        <v>2.456527837997767</v>
+        <v>0.7466946056113</v>
       </c>
       <c r="G8" t="n">
-        <v>2.118994227609772</v>
+        <v>-1.898696227247176</v>
       </c>
       <c r="H8" t="n">
-        <v>3.881091739255998</v>
+        <v>-1.909488879386768</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06043284126426277</v>
+        <v>0.196397992650878</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.317562134416222</v>
+        <v>-1.912259114868077</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3880,37 +5296,37 @@
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7325171433055</v>
       </c>
       <c r="F9" t="n">
-        <v>2.456527837997767</v>
+        <v>0.7319933864281666</v>
       </c>
       <c r="G9" t="n">
-        <v>2.118994227609772</v>
+        <v>0.07155213244331993</v>
       </c>
       <c r="H9" t="n">
-        <v>3.881091739255998</v>
+        <v>1.266860159162003</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06043284126426277</v>
+        <v>0.3327632173860757</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.317562134416222</v>
+        <v>-0.04946314467094115</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sdn</t>
+          <t>geant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3927,37 +5343,37 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>2.508581521084567</v>
+        <v>0.7325171433055</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3989559454172</v>
+        <v>0.7806467503629666</v>
       </c>
       <c r="G10" t="n">
-        <v>4.569720251711495</v>
+        <v>-6.16535033740786</v>
       </c>
       <c r="H10" t="n">
-        <v>7.643016269751377</v>
+        <v>-2.051229914312247</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0166912891669964</v>
+        <v>0.1767069816853496</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>14.13414061635875</v>
+        <v>-0.8862354771538121</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>abilene</t>
+          <t>sdn</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3974,25 +5390,25 @@
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8452595759288</v>
+        <v>2.508581521084567</v>
       </c>
       <c r="F11" t="n">
-        <v>1.847143500100633</v>
+        <v>4.016685571412967</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1019912189676009</v>
+        <v>-37.54598221632489</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.614722278685788</v>
+        <v>-39.30746520066631</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06873597908750025</v>
+        <v>0.0006465893522372362</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.59322570262103</v>
+        <v>-39.40939128165797</v>
       </c>
       <c r="L11" t="n">
         <v>3</v>
@@ -4004,7 +5420,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>abilene</t>
+          <t>sdn</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4021,37 +5437,37 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8452595759288</v>
+        <v>2.508581521084567</v>
       </c>
       <c r="F12" t="n">
-        <v>1.687986454281933</v>
+        <v>3.9476626848196</v>
       </c>
       <c r="G12" t="n">
-        <v>9.31720282754107</v>
+        <v>-36.45400528441544</v>
       </c>
       <c r="H12" t="n">
-        <v>9.562074904403923</v>
+        <v>-44.95555630399251</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01076072148515404</v>
+        <v>0.0004944371081306192</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>7.704106951248733</v>
+        <v>-50.57693709663502</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>abilene</t>
+          <t>sdn</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4068,33 +5484,37 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8452595759288</v>
+        <v>2.508581521084567</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8452595759288</v>
+        <v>2.478177088888334</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+        <v>1.226886986106068</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.714246157832544</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2286179923688734</v>
+      </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2.444055997274246</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>abilene</t>
+          <t>sdn</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4111,25 +5531,25 @@
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>1.741927542336333</v>
+        <v>2.508581521084567</v>
       </c>
       <c r="F14" t="n">
-        <v>1.847143500100633</v>
+        <v>4.016685571412967</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.6961442226101</v>
+        <v>-37.54598221632489</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.624068137728229</v>
+        <v>-39.30746520066631</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01677227991370391</v>
+        <v>0.0006465893522372362</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.16958439644507</v>
+        <v>-39.40939128165797</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -4141,7 +5561,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>abilene</t>
+          <t>sdn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4158,37 +5578,37 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1.741927542336333</v>
+        <v>2.508581521084567</v>
       </c>
       <c r="F15" t="n">
-        <v>1.687986454281933</v>
+        <v>3.9476626848196</v>
       </c>
       <c r="G15" t="n">
-        <v>3.195587732209981</v>
+        <v>-36.45400528441544</v>
       </c>
       <c r="H15" t="n">
-        <v>6.483164150050718</v>
+        <v>-44.95555630399251</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02297498119264761</v>
+        <v>0.0004944371081306192</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.416375606831945</v>
+        <v>-50.57693709663502</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>abilene</t>
+          <t>sdn</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4205,37 +5625,37 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.741927542336333</v>
+        <v>2.508581521084567</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8452595759288</v>
+        <v>2.478177088888334</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.599864373577645</v>
+        <v>1.226886986106068</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.217643933060213</v>
+        <v>1.714246157832544</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01866031098882544</v>
+        <v>0.2286179923688734</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.07928679281325</v>
+        <v>2.444055997274246</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>abilene</t>
+          <t>sdn</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4252,25 +5672,25 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>1.741927542336333</v>
+        <v>2.508581521084567</v>
       </c>
       <c r="F17" t="n">
-        <v>1.648544334619567</v>
+        <v>2.456527837997767</v>
       </c>
       <c r="G17" t="n">
-        <v>5.664585765496954</v>
+        <v>2.118994227609772</v>
       </c>
       <c r="H17" t="n">
-        <v>4.152059365155624</v>
+        <v>3.881091739255998</v>
       </c>
       <c r="I17" t="n">
-        <v>0.05340202909654521</v>
+        <v>0.06043284126426277</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>8.536216975571049</v>
+        <v>5.317562134416222</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4282,7 +5702,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>abilene</t>
+          <t>sdn</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4299,25 +5719,25 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>1.741927542336333</v>
+        <v>2.508581521084567</v>
       </c>
       <c r="F18" t="n">
-        <v>1.701198254674267</v>
+        <v>2.456527837997767</v>
       </c>
       <c r="G18" t="n">
-        <v>2.394152918400727</v>
+        <v>2.118994227609772</v>
       </c>
       <c r="H18" t="n">
-        <v>3.370419643454545</v>
+        <v>3.881091739255998</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07788484463188806</v>
+        <v>0.06043284126426277</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>8.649423375677356</v>
+        <v>5.317562134416222</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4329,47 +5749,466 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>sdn</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rl_sup</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.508581521084567</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.3989559454172</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.569720251711495</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.643016269751377</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0166912891669964</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>14.13414061635875</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>abilene</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>v3_static</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.8452595759288</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.847143500100633</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.1019912189676009</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-3.614722278685788</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.06873597908750025</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-10.59322570262103</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>hedge_v3</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.8452595759288</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.687986454281933</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9.31720282754107</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.562074904403923</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01076072148515404</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.704106951248733</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>static_k4</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.8452595759288</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.8452595759288</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>rl_sac</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>v3_static</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.741927542336333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.847143500100633</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-5.6961442226101</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-7.624068137728229</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01677227991370391</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-11.16958439644507</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>hedge_v3</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.741927542336333</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.687986454281933</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.195587732209981</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.483164150050718</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.02297498119264761</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.416375606831945</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>static_k4</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.741927542336333</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.8452595759288</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-5.599864373577645</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-7.217643933060213</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.01866031098882544</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-11.07928679281325</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>hedge</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.741927542336333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.648544334619567</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.664585765496954</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.152059365155624</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.05340202909654521</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>8.536216975571049</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>hedge_prior</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.741927542336333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.701198254674267</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.394152918400727</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.370419643454545</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.07788484463188806</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8.649423375677356</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>abilene</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>rl_sac</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>rl_sup</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
         <v>1.741927542336333</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F28" t="n">
         <v>1.6984610475666</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G28" t="n">
         <v>2.559169362877523</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H28" t="n">
         <v>5.162870227113843</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I28" t="n">
         <v>0.03552879224579629</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>4.788907840922866</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>3</v>
       </c>
     </row>
